--- a/forms/trg/Formulir_TRG_ddrg.xlsx
+++ b/forms/trg/Formulir_TRG_ddrg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B38)</f>
+        <f>COUNTA(Anggota!B5:B39)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F38)</f>
+        <f>COUNTA(Anggota!F5:F39)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,18 +913,14 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Daud Malamassam, M.Agr</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
+          <t>Prof. Dr. Ir. Syamsu Rijal, S.Hut., M.Si., IPU</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n"/>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Forest Inventory</t>
+          <t>Forest Planning</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -946,18 +942,18 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Roland A. Barkey, M.Sc</t>
+          <t>Prof. Dr. Ir. Daud Malamassam, M.Agr</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Forestry Planning for Regional Development</t>
+          <t>Forest Inventory</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -979,18 +975,18 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Chairil A., S.Hut., M.Hut</t>
+          <t>Dr. Ir. Roland A. Barkey, M.Sc</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Remote sensing of Forestry and environmental</t>
+          <t>Forestry Planning for Regional Development</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1012,18 +1008,18 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Ir. Nasri, S.Hut, M. Hut., Ph.D., IPM</t>
+          <t>Chairil A., S.Hut., M.Hut</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Biogeography</t>
+          <t>Remote sensing of Forestry and environmental</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1045,18 +1041,18 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Nurdin Dalya, S.Hut, M.Hut, Ph.D</t>
+          <t>Ir. Nasri, S.Hut, M. Hut., Ph.D., IPM</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Management of Community Forest Harvesting</t>
+          <t>Biogeography</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1078,18 +1074,18 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Ir. Munajat Nursaputra, S.Hut, M.Sc., IPM</t>
+          <t>Nurdin Dalya, S.Hut, M.Hut, Ph.D</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Geographic information system &amp; Spatial Modelling</t>
+          <t>Management of Community Forest Harvesting</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1111,22 +1107,18 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Mohd Hasmadi Ismail</t>
+          <t>Ir. Munajat Nursaputra, S.Hut, M.Sc., IPM</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Universiti Putra Malaysia</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n"/>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Geoinformatic Technology - Remote Sensing and GIS</t>
+          <t>Geographic information system &amp; Spatial Modelling</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1148,22 +1140,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Samsuri, S.Hut, M.Si, IPU</t>
+          <t>Prof. Dr. Mohd Hasmadi Ismail</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Universitas Sumatra Utara</t>
+          <t>Universiti Putra Malaysia</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Forest Landscape Management</t>
+          <t>Geoinformatic Technology - Remote Sensing and GIS</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1185,22 +1177,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Heni Masruroh, S.Pd, M.Sc</t>
+          <t>Dr. Ir. Samsuri, S.Hut, M.Si, IPU</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Universitas Negeri Malang</t>
+          <t>Universitas Sumatra Utara</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Geographic Information System</t>
+          <t>Forest Landscape Management</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1222,22 +1214,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Prof. Cristoph Kleinn</t>
+          <t>Dr. Heni Masruroh, S.Pd, M.Sc</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>GGeorg-August-University Göttingen, Germany</t>
+          <t>Universitas Negeri Malang</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Forest Inventory and Remote Sensing</t>
+          <t>Geographic Information System</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1259,18 +1251,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Afandi Ahmad, S.Hut., M.Si</t>
+          <t>Prof. Cristoph Kleinn</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>GGeorg-August-University Göttingen, Germany</t>
+        </is>
+      </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Remote Sensing and Spatial Modelling</t>
+          <t>Forest Inventory and Remote Sensing</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1292,22 +1288,18 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Anugrahandini Nasir, S.Hut., M.Si</t>
+          <t>Afandi Ahmad, S.Hut., M.Si</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>Universitas Islam Makassar</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n"/>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Forest Planning</t>
+          <t>Remote Sensing and Spatial Modelling</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1329,16 +1321,24 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Nur Zam zam Putri Ardi, S.Hut</t>
+          <t>Anugrahandini Nasir, S.Hut., M.Si</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="11" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Universitas Islam Makassar</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Forest Planning</t>
+        </is>
+      </c>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Wd. Rischa Widyasari F. Suri, S.Hut</t>
+          <t>Nur Zam zam Putri Ardi, S.Hut</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Revalina Theresia Sinaga, S.Hut</t>
+          <t>Wd. Rischa Widyasari F. Suri, S.Hut</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Fian Afrilla, S.Hut</t>
+          <t>Revalina Theresia Sinaga, S.Hut</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="12" t="n"/>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Josua Pyayoga F. Woof, S.Hut</t>
+          <t>Fian Afrilla, S.Hut</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="12" t="n"/>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Nawwaf Hasbullah, S.Hut</t>
+          <t>Josua Pyayoga F. Woof, S.Hut</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="12" t="n"/>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Nurhidayat, S.Hut</t>
+          <t>Muhammad Nawwaf Hasbullah, S.Hut</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="12" t="n"/>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Helen Natalia Kasang, S.Hut</t>
+          <t>Nurhidayat, S.Hut</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D24" s="12" t="n"/>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Klara Tasik Dawa, S.Hut</t>
+          <t>Helen Natalia Kasang, S.Hut</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Shafira Mutmainnah Asra, S.Hut</t>
+          <t>Klara Tasik Dawa, S.Hut</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D26" s="12" t="n"/>
@@ -1617,9 +1617,21 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Shafira Mutmainnah Asra, S.Hut</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Deforestation and Degradation Research Group (D Forest Grad) are eam research group of Hasanuddin University with research focus on Deforestation - Degradation (Land Cover Changes) &amp; Natural Resource Measurement and Inventory.</t>
+        </is>
+      </c>
       <c r="E27" s="11" t="n"/>
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="12" t="n"/>
@@ -1628,7 +1640,11 @@
       <c r="J27" s="12" t="n"/>
       <c r="K27" s="12" t="n"/>
       <c r="L27" s="12" t="n"/>
-      <c r="M27" s="12" t="n"/>
+      <c r="M27" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -1817,15 +1833,32 @@
       <c r="L38" s="12" t="n"/>
       <c r="M38" s="12" t="n"/>
     </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="12" t="n"/>
+      <c r="G39" s="12" t="n"/>
+      <c r="H39" s="12" t="n"/>
+      <c r="I39" s="12" t="n"/>
+      <c r="J39" s="12" t="n"/>
+      <c r="K39" s="12" t="n"/>
+      <c r="L39" s="12" t="n"/>
+      <c r="M39" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/forms/trg/Formulir_TRG_ddrg.xlsx
+++ b/forms/trg/Formulir_TRG_ddrg.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Ir. Syamsu Rijal, S.Hut., M.Si., IPU</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
